--- a/data/intermediate/ied.xlsx
+++ b/data/intermediate/ied.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -376,7 +376,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>9502.387930250025</v>
+        <v>9502.387930250001</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -387,7 +387,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>17842.31330404016</v>
+        <v>17842.31330404</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -398,7 +398,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>24133.97943056019</v>
+        <v>24133.97943056</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>31604.29417528022</v>
+        <v>31604.29417528</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -431,7 +431,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>18102.44999999985</v>
+        <v>18102.45</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -442,7 +442,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>26055.60837050006</v>
+        <v>26055.6083705</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -453,7 +453,7 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>32921.23555030004</v>
+        <v>32921.2355503</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -464,7 +464,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>10334.03857173006</v>
+        <v>10334.03857173</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -475,7 +475,7 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>17969.26464864999</v>
+        <v>17969.26464865</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -486,7 +486,7 @@
         <v>3</v>
       </c>
       <c r="C12">
-        <v>23482.31883745007</v>
+        <v>23482.31883745</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -497,7 +497,7 @@
         <v>4</v>
       </c>
       <c r="C13">
-        <v>29079.43309080007</v>
+        <v>29079.4330908</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -508,7 +508,7 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>11864.03046281999</v>
+        <v>11864.03046282</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -519,7 +519,7 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>18433.46954255985</v>
+        <v>18433.46954256</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -530,7 +530,7 @@
         <v>3</v>
       </c>
       <c r="C16">
-        <v>24831.72427092007</v>
+        <v>24831.72427092</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -541,7 +541,7 @@
         <v>4</v>
       </c>
       <c r="C17">
-        <v>31621.20435087015</v>
+        <v>31621.20435087</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="C18">
-        <v>19427.45778673005</v>
+        <v>19427.45778673</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -563,7 +563,7 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>27511.62373282995</v>
+        <v>27511.62373283</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -574,7 +574,7 @@
         <v>3</v>
       </c>
       <c r="C20">
-        <v>32147.38886485986</v>
+        <v>32147.38886486</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -585,7 +585,7 @@
         <v>4</v>
       </c>
       <c r="C21">
-        <v>35291.61835650035</v>
+        <v>35291.6183565</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -596,7 +596,7 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>18635.69179056182</v>
+        <v>18635.69179056</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -607,7 +607,7 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>29040.8238745911</v>
+        <v>29040.82387459</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -618,7 +618,7 @@
         <v>3</v>
       </c>
       <c r="C24">
-        <v>32926.43680025823</v>
+        <v>32926.43680026</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -629,7 +629,7 @@
         <v>4</v>
       </c>
       <c r="C25">
-        <v>36058.04377568115</v>
+        <v>36058.04377568</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -640,7 +640,7 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>20312.65875078067</v>
+        <v>20312.65875078</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -651,7 +651,7 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>31096.32510957158</v>
+        <v>31096.32510957</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -662,7 +662,7 @@
         <v>3</v>
       </c>
       <c r="C28">
-        <v>35737.48954061164</v>
+        <v>35737.48954061</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -673,7 +673,7 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>36872.42195115965</v>
+        <v>36872.42195116</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -684,7 +684,7 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>21373.19310550217</v>
+        <v>21373.1931055</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -695,7 +695,7 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>34264.56746296593</v>
+        <v>34264.56746297</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -706,7 +706,7 @@
         <v>3</v>
       </c>
       <c r="C32">
-        <v>40905.61371637016</v>
+        <v>40905.61371637</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -717,7 +717,7 @@
         <v>4</v>
       </c>
       <c r="C33">
-        <v>40870.76932803365</v>
+        <v>40870.76932803</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -728,7 +728,18 @@
         <v>1</v>
       </c>
       <c r="C34">
-        <v>23590.62204554513</v>
+        <v>23590.62204555</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
+        <v>2026</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>34967.54664001</v>
       </c>
     </row>
   </sheetData>
